--- a/sheet-template/Fiskalis-Sheet-Template.xlsx
+++ b/sheet-template/Fiskalis-Sheet-Template.xlsx
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nein. Fiskalis ist ein unabhängiges Verzeichnis und erbringt selbst keine Steuer-, Finanz- oder Rechtsberatung. Wir vermitteln ausschließlich den Kontakt zu geprüften Anbietern.</t>
+          <t>Nein. Fiskalis ist ein unabhängiges Verzeichnis und erbringt selbst keine Steuer-, Finanz- oder Rechtsberatung. Wir vermitteln ausschließlich den Kontakt zu gelisteten Anbietern.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Wie werden Anbieter geprüft?</t>
+          <t>Werden die gelisteten Anbieter von Fiskalis geprüft?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Wir gleichen jeden Anbieter vor Freischaltung gegen ein öffentliches Register ab — mehr dazu unter &lt;a href=&amp;quot;/wie-wir-pruefen/&amp;quot;&gt;Wie wir prüfen&lt;/a&gt;.</t>
+          <t>Nein. Fiskalis ist ein reines Verzeichnis- und Vermittlungsangebot — wir listen Anbieter, prüfen oder zertifizieren aber nicht deren fachliche oder berufsrechtliche Qualifikation. Verlassen Sie sich auf die Bewertungen echter Mandanten und Ihre eigene Recherche.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nein. Jede Bewerbung durchläuft eine Prüfung gegen ein öffentliches Register (Steuerberaterverzeichnis bzw. Vermittlerregister) — mehr dazu unter &lt;a href=&amp;quot;/wie-wir-pruefen/&amp;quot;&gt;Wie wir prüfen&lt;/a&gt;.</t>
+          <t>Nein. Wir behalten uns vor, Anfragen ohne Angabe von Gründen abzulehnen, um die Qualität des Verzeichnisses zu sichern.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
